--- a/data.mn/public/datasets/unemployment-rate-youth.xlsx
+++ b/data.mn/public/datasets/unemployment-rate-youth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,19 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -425,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -446,129 +440,137 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B2" t="n">
-        <v>14.7</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="n">
-        <v>4.7</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B4" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B6" t="n">
-        <v>16.3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B7" t="n">
-        <v>23.9</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B8" t="n">
-        <v>20.4</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B9" t="n">
-        <v>22.7</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B10" t="n">
-        <v>25.1</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B11" t="n">
-        <v>17.9</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B12" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B13" t="n">
-        <v>16.6</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B15" t="n">
-        <v>15.6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B16" t="n">
-        <v>19.5</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B17" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>2009</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>22</v>
       </c>
     </row>
